--- a/input/excel/Profil and ValueSet_Observation_14.01.2026_v4.csv/ObservationCodesVS.xlsx
+++ b/input/excel/Profil and ValueSet_Observation_14.01.2026_v4.csv/ObservationCodesVS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\behzod_axmedov\Desktop\DHP-temp02\ObservationLab\digital-health-ig\input\excel\Profil and ValueSet_Observation_14.01.2026_v4.csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0642AB1B-D773-4E36-B00B-0B6434FA3B9E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4E7FEC7-E07C-4C3C-921F-48B16711541B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1005" yWindow="315" windowWidth="19050" windowHeight="11145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LabResearchsCS" sheetId="1" r:id="rId1"/>
@@ -3539,54 +3539,6 @@
   </si>
   <si>
     <t>lab-242</t>
-  </si>
-  <si>
-    <t>lab-P</t>
-  </si>
-  <si>
-    <t>lab-Q</t>
-  </si>
-  <si>
-    <t>lab-R</t>
-  </si>
-  <si>
-    <t>lab-S</t>
-  </si>
-  <si>
-    <t>lab-T</t>
-  </si>
-  <si>
-    <t>lab-U</t>
-  </si>
-  <si>
-    <t>lab-V</t>
-  </si>
-  <si>
-    <t>lab-W</t>
-  </si>
-  <si>
-    <t>lab-X</t>
-  </si>
-  <si>
-    <t>lab-Y</t>
-  </si>
-  <si>
-    <t>lab-Z</t>
-  </si>
-  <si>
-    <t>lab-AA</t>
-  </si>
-  <si>
-    <t>lab-BB</t>
-  </si>
-  <si>
-    <t>lab-CC</t>
-  </si>
-  <si>
-    <t>lab-DD</t>
-  </si>
-  <si>
-    <t>lab-EE</t>
   </si>
   <si>
     <t>29610-3</t>
@@ -3799,12 +3751,60 @@
   <si>
     <t>Hepatitis B virus e Ab [Presence] in Serum or Plasma</t>
   </si>
+  <si>
+    <t>lab-243</t>
+  </si>
+  <si>
+    <t>lab-244</t>
+  </si>
+  <si>
+    <t>lab-245</t>
+  </si>
+  <si>
+    <t>lab-246</t>
+  </si>
+  <si>
+    <t>lab-247</t>
+  </si>
+  <si>
+    <t>lab-248</t>
+  </si>
+  <si>
+    <t>lab-249</t>
+  </si>
+  <si>
+    <t>lab-250</t>
+  </si>
+  <si>
+    <t>lab-251</t>
+  </si>
+  <si>
+    <t>lab-252</t>
+  </si>
+  <si>
+    <t>lab-253</t>
+  </si>
+  <si>
+    <t>lab-254</t>
+  </si>
+  <si>
+    <t>lab-255</t>
+  </si>
+  <si>
+    <t>lab-256</t>
+  </si>
+  <si>
+    <t>lab-257</t>
+  </si>
+  <si>
+    <t>lab-258</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3883,6 +3883,12 @@
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -3975,12 +3981,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -4008,6 +4008,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -4300,13 +4306,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -4348,7 +4354,7 @@
       <c r="K3" s="4"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="12" t="s">
         <v>916</v>
       </c>
       <c r="B4" s="6" t="s">
@@ -4365,7 +4371,7 @@
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="12" t="s">
         <v>917</v>
       </c>
       <c r="B5" s="6" t="s">
@@ -4382,7 +4388,7 @@
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="12" t="s">
         <v>918</v>
       </c>
       <c r="B6" s="6" t="s">
@@ -4399,7 +4405,7 @@
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="12" t="s">
         <v>919</v>
       </c>
       <c r="B7" s="6" t="s">
@@ -4416,7 +4422,7 @@
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="12" t="s">
         <v>920</v>
       </c>
       <c r="B8" s="6" t="s">
@@ -4433,7 +4439,7 @@
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="12" t="s">
         <v>921</v>
       </c>
       <c r="B9" s="6" t="s">
@@ -4450,7 +4456,7 @@
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="12" t="s">
         <v>922</v>
       </c>
       <c r="B10" s="6" t="s">
@@ -4467,7 +4473,7 @@
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="12" t="s">
         <v>923</v>
       </c>
       <c r="B11" s="6" t="s">
@@ -4484,7 +4490,7 @@
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="12" t="s">
         <v>924</v>
       </c>
       <c r="B12" s="6" t="s">
@@ -4501,7 +4507,7 @@
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="12" t="s">
         <v>925</v>
       </c>
       <c r="B13" s="6" t="s">
@@ -4518,7 +4524,7 @@
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="12" t="s">
         <v>926</v>
       </c>
       <c r="B14" s="6" t="s">
@@ -4535,7 +4541,7 @@
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="12" t="s">
         <v>927</v>
       </c>
       <c r="B15" s="6" t="s">
@@ -4552,7 +4558,7 @@
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="12" t="s">
         <v>928</v>
       </c>
       <c r="B16" s="6" t="s">
@@ -4569,7 +4575,7 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="12" t="s">
         <v>929</v>
       </c>
       <c r="B17" s="6" t="s">
@@ -4586,7 +4592,7 @@
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="12" t="s">
         <v>930</v>
       </c>
       <c r="B18" s="6" t="s">
@@ -4603,7 +4609,7 @@
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="12" t="s">
         <v>931</v>
       </c>
       <c r="B19" s="6" t="s">
@@ -4620,7 +4626,7 @@
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
+      <c r="A20" s="12" t="s">
         <v>932</v>
       </c>
       <c r="B20" s="6" t="s">
@@ -4637,7 +4643,7 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="12" t="s">
         <v>933</v>
       </c>
       <c r="B21" s="6" t="s">
@@ -4654,7 +4660,7 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="12" t="s">
         <v>934</v>
       </c>
       <c r="B22" s="6" t="s">
@@ -4671,7 +4677,7 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
+      <c r="A23" s="12" t="s">
         <v>935</v>
       </c>
       <c r="B23" s="6" t="s">
@@ -4688,7 +4694,7 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
+      <c r="A24" s="12" t="s">
         <v>936</v>
       </c>
       <c r="B24" s="6" t="s">
@@ -4705,7 +4711,7 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="14" t="s">
+      <c r="A25" s="12" t="s">
         <v>937</v>
       </c>
       <c r="B25" s="6" t="s">
@@ -4722,7 +4728,7 @@
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
+      <c r="A26" s="12" t="s">
         <v>938</v>
       </c>
       <c r="B26" s="6" t="s">
@@ -4739,7 +4745,7 @@
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="14" t="s">
+      <c r="A27" s="12" t="s">
         <v>939</v>
       </c>
       <c r="B27" s="6" t="s">
@@ -4756,7 +4762,7 @@
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="14" t="s">
+      <c r="A28" s="12" t="s">
         <v>940</v>
       </c>
       <c r="B28" s="6" t="s">
@@ -4773,7 +4779,7 @@
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="14" t="s">
+      <c r="A29" s="12" t="s">
         <v>941</v>
       </c>
       <c r="B29" s="6" t="s">
@@ -4790,7 +4796,7 @@
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="14" t="s">
+      <c r="A30" s="12" t="s">
         <v>942</v>
       </c>
       <c r="B30" s="6" t="s">
@@ -4807,7 +4813,7 @@
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="15" t="s">
+      <c r="A31" s="13" t="s">
         <v>943</v>
       </c>
       <c r="B31" s="6" t="s">
@@ -4824,7 +4830,7 @@
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="14" t="s">
+      <c r="A32" s="12" t="s">
         <v>944</v>
       </c>
       <c r="B32" s="6" t="s">
@@ -4841,7 +4847,7 @@
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="14" t="s">
+      <c r="A33" s="12" t="s">
         <v>945</v>
       </c>
       <c r="B33" s="6" t="s">
@@ -4858,7 +4864,7 @@
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="14" t="s">
+      <c r="A34" s="12" t="s">
         <v>946</v>
       </c>
       <c r="B34" s="6" t="s">
@@ -4875,7 +4881,7 @@
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="14" t="s">
+      <c r="A35" s="12" t="s">
         <v>947</v>
       </c>
       <c r="B35" s="6" t="s">
@@ -4892,7 +4898,7 @@
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="14" t="s">
+      <c r="A36" s="12" t="s">
         <v>948</v>
       </c>
       <c r="B36" s="6" t="s">
@@ -4909,7 +4915,7 @@
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="14" t="s">
+      <c r="A37" s="12" t="s">
         <v>949</v>
       </c>
       <c r="B37" s="6" t="s">
@@ -4926,7 +4932,7 @@
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="14" t="s">
+      <c r="A38" s="12" t="s">
         <v>950</v>
       </c>
       <c r="B38" s="6" t="s">
@@ -4943,7 +4949,7 @@
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="14" t="s">
+      <c r="A39" s="12" t="s">
         <v>951</v>
       </c>
       <c r="B39" s="6" t="s">
@@ -4960,7 +4966,7 @@
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="14" t="s">
+      <c r="A40" s="12" t="s">
         <v>952</v>
       </c>
       <c r="B40" s="6" t="s">
@@ -4977,7 +4983,7 @@
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="14" t="s">
+      <c r="A41" s="12" t="s">
         <v>953</v>
       </c>
       <c r="B41" s="6" t="s">
@@ -4994,7 +5000,7 @@
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="14" t="s">
+      <c r="A42" s="12" t="s">
         <v>954</v>
       </c>
       <c r="B42" s="6" t="s">
@@ -5011,7 +5017,7 @@
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="14" t="s">
+      <c r="A43" s="12" t="s">
         <v>955</v>
       </c>
       <c r="B43" s="6" t="s">
@@ -5028,7 +5034,7 @@
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="14" t="s">
+      <c r="A44" s="12" t="s">
         <v>956</v>
       </c>
       <c r="B44" s="6" t="s">
@@ -5045,7 +5051,7 @@
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="14" t="s">
+      <c r="A45" s="12" t="s">
         <v>957</v>
       </c>
       <c r="B45" s="6" t="s">
@@ -5062,7 +5068,7 @@
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="16" t="s">
+      <c r="A46" s="14" t="s">
         <v>958</v>
       </c>
       <c r="B46" s="6" t="s">
@@ -5079,7 +5085,7 @@
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="14" t="s">
+      <c r="A47" s="12" t="s">
         <v>959</v>
       </c>
       <c r="B47" s="6" t="s">
@@ -5096,7 +5102,7 @@
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="14" t="s">
+      <c r="A48" s="12" t="s">
         <v>960</v>
       </c>
       <c r="B48" s="6" t="s">
@@ -5113,7 +5119,7 @@
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="14" t="s">
+      <c r="A49" s="12" t="s">
         <v>961</v>
       </c>
       <c r="B49" s="6" t="s">
@@ -5130,7 +5136,7 @@
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="14" t="s">
+      <c r="A50" s="12" t="s">
         <v>962</v>
       </c>
       <c r="B50" s="6" t="s">
@@ -5147,7 +5153,7 @@
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="14" t="s">
+      <c r="A51" s="12" t="s">
         <v>963</v>
       </c>
       <c r="B51" s="6" t="s">
@@ -5164,7 +5170,7 @@
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="14" t="s">
+      <c r="A52" s="12" t="s">
         <v>964</v>
       </c>
       <c r="B52" s="6" t="s">
@@ -5181,7 +5187,7 @@
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="16" t="s">
+      <c r="A53" s="14" t="s">
         <v>965</v>
       </c>
       <c r="B53" s="5"/>
@@ -5196,7 +5202,7 @@
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="14" t="s">
+      <c r="A54" s="12" t="s">
         <v>964</v>
       </c>
       <c r="B54" s="6" t="s">
@@ -5213,7 +5219,7 @@
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="14" t="s">
+      <c r="A55" s="12" t="s">
         <v>966</v>
       </c>
       <c r="B55" s="6" t="s">
@@ -5230,7 +5236,7 @@
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="14" t="s">
+      <c r="A56" s="12" t="s">
         <v>967</v>
       </c>
       <c r="B56" s="6" t="s">
@@ -5247,7 +5253,7 @@
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="14" t="s">
+      <c r="A57" s="12" t="s">
         <v>968</v>
       </c>
       <c r="B57" s="6" t="s">
@@ -5264,7 +5270,7 @@
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="14" t="s">
+      <c r="A58" s="12" t="s">
         <v>969</v>
       </c>
       <c r="B58" s="6" t="s">
@@ -5281,7 +5287,7 @@
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="14" t="s">
+      <c r="A59" s="12" t="s">
         <v>970</v>
       </c>
       <c r="B59" s="6" t="s">
@@ -5298,7 +5304,7 @@
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="14" t="s">
+      <c r="A60" s="12" t="s">
         <v>971</v>
       </c>
       <c r="B60" s="6" t="s">
@@ -5315,7 +5321,7 @@
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="14" t="s">
+      <c r="A61" s="12" t="s">
         <v>972</v>
       </c>
       <c r="B61" s="6" t="s">
@@ -5332,7 +5338,7 @@
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="14" t="s">
+      <c r="A62" s="12" t="s">
         <v>973</v>
       </c>
       <c r="B62" s="6" t="s">
@@ -5349,7 +5355,7 @@
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="14" t="s">
+      <c r="A63" s="12" t="s">
         <v>974</v>
       </c>
       <c r="B63" s="6" t="s">
@@ -5366,7 +5372,7 @@
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="14" t="s">
+      <c r="A64" s="12" t="s">
         <v>975</v>
       </c>
       <c r="B64" s="6" t="s">
@@ -5383,7 +5389,7 @@
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="14" t="s">
+      <c r="A65" s="12" t="s">
         <v>976</v>
       </c>
       <c r="B65" s="6" t="s">
@@ -5400,7 +5406,7 @@
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="14" t="s">
+      <c r="A66" s="12" t="s">
         <v>977</v>
       </c>
       <c r="B66" s="6" t="s">
@@ -5417,7 +5423,7 @@
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="14" t="s">
+      <c r="A67" s="12" t="s">
         <v>978</v>
       </c>
       <c r="B67" s="6" t="s">
@@ -5434,7 +5440,7 @@
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="14" t="s">
+      <c r="A68" s="12" t="s">
         <v>979</v>
       </c>
       <c r="B68" s="6" t="s">
@@ -5451,7 +5457,7 @@
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="14" t="s">
+      <c r="A69" s="12" t="s">
         <v>980</v>
       </c>
       <c r="B69" s="6" t="s">
@@ -5468,7 +5474,7 @@
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="14" t="s">
+      <c r="A70" s="12" t="s">
         <v>981</v>
       </c>
       <c r="B70" s="6" t="s">
@@ -5485,7 +5491,7 @@
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="14" t="s">
+      <c r="A71" s="12" t="s">
         <v>982</v>
       </c>
       <c r="B71" s="9" t="s">
@@ -5502,7 +5508,7 @@
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="14" t="s">
+      <c r="A72" s="12" t="s">
         <v>983</v>
       </c>
       <c r="B72" s="9" t="s">
@@ -5519,7 +5525,7 @@
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="14" t="s">
+      <c r="A73" s="12" t="s">
         <v>984</v>
       </c>
       <c r="B73" s="9" t="s">
@@ -5536,7 +5542,7 @@
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="14" t="s">
+      <c r="A74" s="12" t="s">
         <v>985</v>
       </c>
       <c r="B74" s="9" t="s">
@@ -5553,7 +5559,7 @@
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="14" t="s">
+      <c r="A75" s="12" t="s">
         <v>986</v>
       </c>
       <c r="B75" s="9" t="s">
@@ -5570,7 +5576,7 @@
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" s="16" t="s">
+      <c r="A76" s="14" t="s">
         <v>987</v>
       </c>
       <c r="B76" s="9" t="s">
@@ -5587,7 +5593,7 @@
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="14" t="s">
+      <c r="A77" s="12" t="s">
         <v>988</v>
       </c>
       <c r="B77" s="6" t="s">
@@ -5604,7 +5610,7 @@
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="14" t="s">
+      <c r="A78" s="12" t="s">
         <v>989</v>
       </c>
       <c r="B78" s="6" t="s">
@@ -5621,7 +5627,7 @@
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="14" t="s">
+      <c r="A79" s="12" t="s">
         <v>990</v>
       </c>
       <c r="B79" s="6" t="s">
@@ -5638,7 +5644,7 @@
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="14" t="s">
+      <c r="A80" s="12" t="s">
         <v>991</v>
       </c>
       <c r="B80" s="6" t="s">
@@ -5655,7 +5661,7 @@
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="14" t="s">
+      <c r="A81" s="12" t="s">
         <v>992</v>
       </c>
       <c r="B81" s="6" t="s">
@@ -5672,7 +5678,7 @@
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="14" t="s">
+      <c r="A82" s="12" t="s">
         <v>993</v>
       </c>
       <c r="B82" s="6" t="s">
@@ -5689,7 +5695,7 @@
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="14" t="s">
+      <c r="A83" s="12" t="s">
         <v>994</v>
       </c>
       <c r="B83" s="6" t="s">
@@ -5706,7 +5712,7 @@
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="14" t="s">
+      <c r="A84" s="12" t="s">
         <v>995</v>
       </c>
       <c r="B84" s="6" t="s">
@@ -5723,7 +5729,7 @@
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" s="14" t="s">
+      <c r="A85" s="12" t="s">
         <v>996</v>
       </c>
       <c r="B85" s="6" t="s">
@@ -5740,7 +5746,7 @@
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" s="14" t="s">
+      <c r="A86" s="12" t="s">
         <v>997</v>
       </c>
       <c r="B86" s="6" t="s">
@@ -5757,7 +5763,7 @@
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" s="14" t="s">
+      <c r="A87" s="12" t="s">
         <v>998</v>
       </c>
       <c r="B87" s="6" t="s">
@@ -5774,7 +5780,7 @@
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" s="14" t="s">
+      <c r="A88" s="12" t="s">
         <v>999</v>
       </c>
       <c r="B88" s="6" t="s">
@@ -5791,7 +5797,7 @@
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" s="17" t="s">
+      <c r="A89" s="15" t="s">
         <v>1000</v>
       </c>
       <c r="B89" s="9" t="s">
@@ -5808,7 +5814,7 @@
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" s="14" t="s">
+      <c r="A90" s="12" t="s">
         <v>1001</v>
       </c>
       <c r="B90" s="6" t="s">
@@ -5825,7 +5831,7 @@
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" s="14" t="s">
+      <c r="A91" s="12" t="s">
         <v>1002</v>
       </c>
       <c r="B91" s="6" t="s">
@@ -5842,7 +5848,7 @@
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" s="14" t="s">
+      <c r="A92" s="12" t="s">
         <v>1003</v>
       </c>
       <c r="B92" s="6" t="s">
@@ -5859,7 +5865,7 @@
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" s="14" t="s">
+      <c r="A93" s="12" t="s">
         <v>1004</v>
       </c>
       <c r="B93" s="6" t="s">
@@ -5876,7 +5882,7 @@
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" s="14" t="s">
+      <c r="A94" s="12" t="s">
         <v>1005</v>
       </c>
       <c r="B94" s="6" t="s">
@@ -5893,7 +5899,7 @@
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" s="14" t="s">
+      <c r="A95" s="12" t="s">
         <v>1006</v>
       </c>
       <c r="B95" s="6" t="s">
@@ -5910,7 +5916,7 @@
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" s="14" t="s">
+      <c r="A96" s="12" t="s">
         <v>1007</v>
       </c>
       <c r="B96" s="6" t="s">
@@ -5927,7 +5933,7 @@
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" s="14" t="s">
+      <c r="A97" s="12" t="s">
         <v>1008</v>
       </c>
       <c r="B97" s="6" t="s">
@@ -5944,7 +5950,7 @@
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="14" t="s">
+      <c r="A98" s="12" t="s">
         <v>1009</v>
       </c>
       <c r="B98" s="6" t="s">
@@ -5961,7 +5967,7 @@
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="14" t="s">
+      <c r="A99" s="12" t="s">
         <v>1010</v>
       </c>
       <c r="B99" s="6" t="s">
@@ -5978,7 +5984,7 @@
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="14" t="s">
+      <c r="A100" s="12" t="s">
         <v>1011</v>
       </c>
       <c r="B100" s="6" t="s">
@@ -5995,7 +6001,7 @@
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" s="14" t="s">
+      <c r="A101" s="12" t="s">
         <v>1012</v>
       </c>
       <c r="B101" s="6" t="s">
@@ -6012,7 +6018,7 @@
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="14" t="s">
+      <c r="A102" s="12" t="s">
         <v>1013</v>
       </c>
       <c r="B102" s="6" t="s">
@@ -6029,7 +6035,7 @@
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103" s="14" t="s">
+      <c r="A103" s="12" t="s">
         <v>1014</v>
       </c>
       <c r="B103" s="6" t="s">
@@ -6046,7 +6052,7 @@
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104" s="14" t="s">
+      <c r="A104" s="12" t="s">
         <v>1015</v>
       </c>
       <c r="B104" s="6" t="s">
@@ -6063,7 +6069,7 @@
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" s="16" t="s">
+      <c r="A105" s="14" t="s">
         <v>1016</v>
       </c>
       <c r="B105" s="6" t="s">
@@ -6080,7 +6086,7 @@
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106" s="14" t="s">
+      <c r="A106" s="12" t="s">
         <v>1017</v>
       </c>
       <c r="B106" s="6" t="s">
@@ -6097,7 +6103,7 @@
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A107" s="14" t="s">
+      <c r="A107" s="12" t="s">
         <v>1018</v>
       </c>
       <c r="B107" s="6" t="s">
@@ -6114,7 +6120,7 @@
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108" s="14" t="s">
+      <c r="A108" s="12" t="s">
         <v>1019</v>
       </c>
       <c r="B108" s="6" t="s">
@@ -6131,7 +6137,7 @@
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A109" s="14" t="s">
+      <c r="A109" s="12" t="s">
         <v>1020</v>
       </c>
       <c r="B109" s="6" t="s">
@@ -6148,7 +6154,7 @@
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A110" s="14" t="s">
+      <c r="A110" s="12" t="s">
         <v>1021</v>
       </c>
       <c r="B110" s="6" t="s">
@@ -6165,7 +6171,7 @@
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111" s="14" t="s">
+      <c r="A111" s="12" t="s">
         <v>1022</v>
       </c>
       <c r="B111" s="6" t="s">
@@ -6182,7 +6188,7 @@
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A112" s="14" t="s">
+      <c r="A112" s="12" t="s">
         <v>1023</v>
       </c>
       <c r="B112" s="6" t="s">
@@ -6199,7 +6205,7 @@
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A113" s="14" t="s">
+      <c r="A113" s="12" t="s">
         <v>1024</v>
       </c>
       <c r="B113" s="6" t="s">
@@ -6216,7 +6222,7 @@
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A114" s="14" t="s">
+      <c r="A114" s="12" t="s">
         <v>1025</v>
       </c>
       <c r="B114" s="6" t="s">
@@ -6233,7 +6239,7 @@
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" s="14" t="s">
+      <c r="A115" s="12" t="s">
         <v>1026</v>
       </c>
       <c r="B115" s="6" t="s">
@@ -6250,7 +6256,7 @@
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A116" s="14" t="s">
+      <c r="A116" s="12" t="s">
         <v>1027</v>
       </c>
       <c r="B116" s="6" t="s">
@@ -6267,7 +6273,7 @@
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A117" s="14" t="s">
+      <c r="A117" s="12" t="s">
         <v>1028</v>
       </c>
       <c r="B117" s="6" t="s">
@@ -6284,7 +6290,7 @@
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A118" s="14" t="s">
+      <c r="A118" s="12" t="s">
         <v>1029</v>
       </c>
       <c r="B118" s="6" t="s">
@@ -6301,7 +6307,7 @@
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A119" s="14" t="s">
+      <c r="A119" s="12" t="s">
         <v>1030</v>
       </c>
       <c r="B119" s="6" t="s">
@@ -6318,7 +6324,7 @@
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A120" s="14" t="s">
+      <c r="A120" s="12" t="s">
         <v>1031</v>
       </c>
       <c r="B120" s="6" t="s">
@@ -6335,7 +6341,7 @@
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A121" s="14" t="s">
+      <c r="A121" s="12" t="s">
         <v>1032</v>
       </c>
       <c r="B121" s="6" t="s">
@@ -6352,7 +6358,7 @@
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A122" s="14" t="s">
+      <c r="A122" s="12" t="s">
         <v>1033</v>
       </c>
       <c r="B122" s="6" t="s">
@@ -6369,7 +6375,7 @@
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A123" s="14" t="s">
+      <c r="A123" s="12" t="s">
         <v>1034</v>
       </c>
       <c r="B123" s="6" t="s">
@@ -6386,7 +6392,7 @@
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A124" s="14" t="s">
+      <c r="A124" s="12" t="s">
         <v>1035</v>
       </c>
       <c r="B124" s="6" t="s">
@@ -6403,7 +6409,7 @@
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A125" s="14" t="s">
+      <c r="A125" s="12" t="s">
         <v>1036</v>
       </c>
       <c r="B125" s="6" t="s">
@@ -6420,7 +6426,7 @@
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A126" s="14" t="s">
+      <c r="A126" s="12" t="s">
         <v>1037</v>
       </c>
       <c r="B126" s="6" t="s">
@@ -6437,7 +6443,7 @@
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A127" s="14" t="s">
+      <c r="A127" s="12" t="s">
         <v>1038</v>
       </c>
       <c r="B127" s="6" t="s">
@@ -6454,7 +6460,7 @@
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A128" s="16" t="s">
+      <c r="A128" s="14" t="s">
         <v>1039</v>
       </c>
       <c r="B128" s="6" t="s">
@@ -6471,7 +6477,7 @@
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129" s="14" t="s">
+      <c r="A129" s="12" t="s">
         <v>1040</v>
       </c>
       <c r="B129" s="6" t="s">
@@ -6488,7 +6494,7 @@
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130" s="14" t="s">
+      <c r="A130" s="12" t="s">
         <v>1041</v>
       </c>
       <c r="B130" s="6" t="s">
@@ -6505,7 +6511,7 @@
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A131" s="14" t="s">
+      <c r="A131" s="12" t="s">
         <v>1042</v>
       </c>
       <c r="B131" s="6" t="s">
@@ -6522,7 +6528,7 @@
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A132" s="14" t="s">
+      <c r="A132" s="12" t="s">
         <v>1043</v>
       </c>
       <c r="B132" s="6" t="s">
@@ -6539,7 +6545,7 @@
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A133" s="14" t="s">
+      <c r="A133" s="12" t="s">
         <v>1044</v>
       </c>
       <c r="B133" s="6" t="s">
@@ -6556,7 +6562,7 @@
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A134" s="14" t="s">
+      <c r="A134" s="12" t="s">
         <v>1045</v>
       </c>
       <c r="B134" s="6" t="s">
@@ -6573,7 +6579,7 @@
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A135" s="14" t="s">
+      <c r="A135" s="12" t="s">
         <v>1046</v>
       </c>
       <c r="B135" s="6" t="s">
@@ -6590,7 +6596,7 @@
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A136" s="14" t="s">
+      <c r="A136" s="12" t="s">
         <v>1047</v>
       </c>
       <c r="B136" s="6" t="s">
@@ -6607,7 +6613,7 @@
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A137" s="14" t="s">
+      <c r="A137" s="12" t="s">
         <v>1048</v>
       </c>
       <c r="B137" s="6" t="s">
@@ -6624,7 +6630,7 @@
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A138" s="14" t="s">
+      <c r="A138" s="12" t="s">
         <v>1049</v>
       </c>
       <c r="B138" s="6" t="s">
@@ -6641,7 +6647,7 @@
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A139" s="14" t="s">
+      <c r="A139" s="12" t="s">
         <v>1050</v>
       </c>
       <c r="B139" s="6" t="s">
@@ -6658,7 +6664,7 @@
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A140" s="16" t="s">
+      <c r="A140" s="14" t="s">
         <v>1051</v>
       </c>
       <c r="B140" s="6" t="s">
@@ -6675,7 +6681,7 @@
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A141" s="14" t="s">
+      <c r="A141" s="12" t="s">
         <v>1052</v>
       </c>
       <c r="B141" s="6" t="s">
@@ -6692,7 +6698,7 @@
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A142" s="14" t="s">
+      <c r="A142" s="12" t="s">
         <v>1053</v>
       </c>
       <c r="B142" s="6" t="s">
@@ -6709,7 +6715,7 @@
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A143" s="14" t="s">
+      <c r="A143" s="12" t="s">
         <v>1054</v>
       </c>
       <c r="B143" s="6" t="s">
@@ -6726,7 +6732,7 @@
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A144" s="14" t="s">
+      <c r="A144" s="12" t="s">
         <v>1055</v>
       </c>
       <c r="B144" s="6" t="s">
@@ -6743,7 +6749,7 @@
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A145" s="14" t="s">
+      <c r="A145" s="12" t="s">
         <v>1056</v>
       </c>
       <c r="B145" s="6" t="s">
@@ -6760,7 +6766,7 @@
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A146" s="14" t="s">
+      <c r="A146" s="12" t="s">
         <v>1057</v>
       </c>
       <c r="B146" s="6" t="s">
@@ -6777,7 +6783,7 @@
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A147" s="14" t="s">
+      <c r="A147" s="12" t="s">
         <v>1058</v>
       </c>
       <c r="B147" s="6" t="s">
@@ -6794,7 +6800,7 @@
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A148" s="14" t="s">
+      <c r="A148" s="12" t="s">
         <v>1059</v>
       </c>
       <c r="B148" s="6" t="s">
@@ -6811,7 +6817,7 @@
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A149" s="14" t="s">
+      <c r="A149" s="12" t="s">
         <v>1060</v>
       </c>
       <c r="B149" s="6" t="s">
@@ -6828,7 +6834,7 @@
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A150" s="14" t="s">
+      <c r="A150" s="12" t="s">
         <v>1061</v>
       </c>
       <c r="B150" s="6" t="s">
@@ -6845,7 +6851,7 @@
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A151" s="14" t="s">
+      <c r="A151" s="12" t="s">
         <v>1062</v>
       </c>
       <c r="B151" s="6" t="s">
@@ -6862,7 +6868,7 @@
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A152" s="14" t="s">
+      <c r="A152" s="12" t="s">
         <v>1063</v>
       </c>
       <c r="B152" s="6" t="s">
@@ -6879,7 +6885,7 @@
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A153" s="14" t="s">
+      <c r="A153" s="12" t="s">
         <v>1064</v>
       </c>
       <c r="B153" s="6" t="s">
@@ -6896,7 +6902,7 @@
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A154" s="14" t="s">
+      <c r="A154" s="12" t="s">
         <v>1065</v>
       </c>
       <c r="B154" s="6" t="s">
@@ -6913,7 +6919,7 @@
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A155" s="14" t="s">
+      <c r="A155" s="12" t="s">
         <v>1066</v>
       </c>
       <c r="B155" s="6" t="s">
@@ -6930,7 +6936,7 @@
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A156" s="14" t="s">
+      <c r="A156" s="12" t="s">
         <v>1067</v>
       </c>
       <c r="B156" s="6" t="s">
@@ -6947,7 +6953,7 @@
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A157" s="14" t="s">
+      <c r="A157" s="12" t="s">
         <v>1068</v>
       </c>
       <c r="B157" s="6" t="s">
@@ -6964,7 +6970,7 @@
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A158" s="14" t="s">
+      <c r="A158" s="12" t="s">
         <v>1069</v>
       </c>
       <c r="B158" s="6" t="s">
@@ -6981,7 +6987,7 @@
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A159" s="14" t="s">
+      <c r="A159" s="12" t="s">
         <v>1070</v>
       </c>
       <c r="B159" s="6" t="s">
@@ -6998,7 +7004,7 @@
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A160" s="16" t="s">
+      <c r="A160" s="14" t="s">
         <v>1071</v>
       </c>
       <c r="B160" s="6" t="s">
@@ -7015,7 +7021,7 @@
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A161" s="14" t="s">
+      <c r="A161" s="12" t="s">
         <v>1072</v>
       </c>
       <c r="B161" s="6" t="s">
@@ -7032,7 +7038,7 @@
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A162" s="14" t="s">
+      <c r="A162" s="12" t="s">
         <v>1073</v>
       </c>
       <c r="B162" s="6" t="s">
@@ -7049,7 +7055,7 @@
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A163" s="14" t="s">
+      <c r="A163" s="12" t="s">
         <v>1074</v>
       </c>
       <c r="B163" s="6" t="s">
@@ -7066,7 +7072,7 @@
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A164" s="14" t="s">
+      <c r="A164" s="12" t="s">
         <v>1075</v>
       </c>
       <c r="B164" s="6" t="s">
@@ -7083,7 +7089,7 @@
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A165" s="14" t="s">
+      <c r="A165" s="12" t="s">
         <v>1076</v>
       </c>
       <c r="B165" s="6" t="s">
@@ -7100,7 +7106,7 @@
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A166" s="14" t="s">
+      <c r="A166" s="12" t="s">
         <v>1077</v>
       </c>
       <c r="B166" s="6" t="s">
@@ -7117,7 +7123,7 @@
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A167" s="14" t="s">
+      <c r="A167" s="12" t="s">
         <v>1078</v>
       </c>
       <c r="B167" s="6" t="s">
@@ -7134,7 +7140,7 @@
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A168" s="14" t="s">
+      <c r="A168" s="12" t="s">
         <v>1079</v>
       </c>
       <c r="B168" s="6" t="s">
@@ -7151,7 +7157,7 @@
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A169" s="14" t="s">
+      <c r="A169" s="12" t="s">
         <v>1080</v>
       </c>
       <c r="B169" s="6" t="s">
@@ -7168,7 +7174,7 @@
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A170" s="14" t="s">
+      <c r="A170" s="12" t="s">
         <v>1081</v>
       </c>
       <c r="B170" s="6" t="s">
@@ -7185,7 +7191,7 @@
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A171" s="14" t="s">
+      <c r="A171" s="12" t="s">
         <v>1082</v>
       </c>
       <c r="B171" s="6" t="s">
@@ -7202,7 +7208,7 @@
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A172" s="14" t="s">
+      <c r="A172" s="12" t="s">
         <v>1083</v>
       </c>
       <c r="B172" s="6" t="s">
@@ -7219,7 +7225,7 @@
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A173" s="14" t="s">
+      <c r="A173" s="12" t="s">
         <v>1084</v>
       </c>
       <c r="B173" s="6" t="s">
@@ -7236,7 +7242,7 @@
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A174" s="14" t="s">
+      <c r="A174" s="12" t="s">
         <v>1085</v>
       </c>
       <c r="B174" s="6" t="s">
@@ -7253,7 +7259,7 @@
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A175" s="14" t="s">
+      <c r="A175" s="12" t="s">
         <v>1086</v>
       </c>
       <c r="B175" s="6" t="s">
@@ -7270,7 +7276,7 @@
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A176" s="14" t="s">
+      <c r="A176" s="12" t="s">
         <v>1087</v>
       </c>
       <c r="B176" s="6" t="s">
@@ -7287,7 +7293,7 @@
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A177" s="14" t="s">
+      <c r="A177" s="12" t="s">
         <v>1088</v>
       </c>
       <c r="B177" s="6" t="s">
@@ -7304,7 +7310,7 @@
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A178" s="14" t="s">
+      <c r="A178" s="12" t="s">
         <v>1089</v>
       </c>
       <c r="B178" s="6" t="s">
@@ -7321,7 +7327,7 @@
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A179" s="14" t="s">
+      <c r="A179" s="12" t="s">
         <v>1090</v>
       </c>
       <c r="B179" s="6" t="s">
@@ -7338,7 +7344,7 @@
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A180" s="14" t="s">
+      <c r="A180" s="12" t="s">
         <v>1091</v>
       </c>
       <c r="B180" s="6" t="s">
@@ -7355,7 +7361,7 @@
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A181" s="16" t="s">
+      <c r="A181" s="14" t="s">
         <v>1092</v>
       </c>
       <c r="B181" s="6" t="s">
@@ -7372,7 +7378,7 @@
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A182" s="14" t="s">
+      <c r="A182" s="12" t="s">
         <v>1093</v>
       </c>
       <c r="B182" s="6" t="s">
@@ -7389,7 +7395,7 @@
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A183" s="14" t="s">
+      <c r="A183" s="12" t="s">
         <v>1094</v>
       </c>
       <c r="B183" s="6" t="s">
@@ -7406,7 +7412,7 @@
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A184" s="14" t="s">
+      <c r="A184" s="12" t="s">
         <v>1095</v>
       </c>
       <c r="B184" s="6" t="s">
@@ -7423,7 +7429,7 @@
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A185" s="14" t="s">
+      <c r="A185" s="12" t="s">
         <v>1096</v>
       </c>
       <c r="B185" s="6" t="s">
@@ -7440,7 +7446,7 @@
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A186" s="14" t="s">
+      <c r="A186" s="12" t="s">
         <v>1097</v>
       </c>
       <c r="B186" s="6" t="s">
@@ -7457,7 +7463,7 @@
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A187" s="14" t="s">
+      <c r="A187" s="12" t="s">
         <v>1098</v>
       </c>
       <c r="B187" s="6" t="s">
@@ -7474,7 +7480,7 @@
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A188" s="14" t="s">
+      <c r="A188" s="12" t="s">
         <v>1099</v>
       </c>
       <c r="B188" s="6" t="s">
@@ -7491,7 +7497,7 @@
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A189" s="14" t="s">
+      <c r="A189" s="12" t="s">
         <v>1100</v>
       </c>
       <c r="B189" s="6" t="s">
@@ -7508,7 +7514,7 @@
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A190" s="14" t="s">
+      <c r="A190" s="12" t="s">
         <v>1101</v>
       </c>
       <c r="B190" s="6" t="s">
@@ -7525,7 +7531,7 @@
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A191" s="14" t="s">
+      <c r="A191" s="12" t="s">
         <v>1102</v>
       </c>
       <c r="B191" s="6" t="s">
@@ -7542,7 +7548,7 @@
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A192" s="14" t="s">
+      <c r="A192" s="12" t="s">
         <v>1103</v>
       </c>
       <c r="B192" s="6" t="s">
@@ -7559,7 +7565,7 @@
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A193" s="14" t="s">
+      <c r="A193" s="12" t="s">
         <v>1104</v>
       </c>
       <c r="B193" s="6" t="s">
@@ -7576,7 +7582,7 @@
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A194" s="14" t="s">
+      <c r="A194" s="12" t="s">
         <v>1105</v>
       </c>
       <c r="B194" s="6" t="s">
@@ -7593,7 +7599,7 @@
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A195" s="14" t="s">
+      <c r="A195" s="12" t="s">
         <v>1106</v>
       </c>
       <c r="B195" s="6" t="s">
@@ -7610,7 +7616,7 @@
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A196" s="14" t="s">
+      <c r="A196" s="12" t="s">
         <v>1107</v>
       </c>
       <c r="B196" s="6" t="s">
@@ -7627,7 +7633,7 @@
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A197" s="16" t="s">
+      <c r="A197" s="14" t="s">
         <v>1108</v>
       </c>
       <c r="B197" s="6" t="s">
@@ -7644,7 +7650,7 @@
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A198" s="14" t="s">
+      <c r="A198" s="12" t="s">
         <v>1109</v>
       </c>
       <c r="B198" s="6" t="s">
@@ -7661,7 +7667,7 @@
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A199" s="14" t="s">
+      <c r="A199" s="12" t="s">
         <v>1110</v>
       </c>
       <c r="B199" s="6" t="s">
@@ -7678,7 +7684,7 @@
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A200" s="14" t="s">
+      <c r="A200" s="12" t="s">
         <v>1111</v>
       </c>
       <c r="B200" s="6" t="s">
@@ -7695,7 +7701,7 @@
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A201" s="14" t="s">
+      <c r="A201" s="12" t="s">
         <v>1112</v>
       </c>
       <c r="B201" s="6" t="s">
@@ -7712,7 +7718,7 @@
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A202" s="14" t="s">
+      <c r="A202" s="12" t="s">
         <v>1113</v>
       </c>
       <c r="B202" s="6" t="s">
@@ -7729,7 +7735,7 @@
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A203" s="16" t="s">
+      <c r="A203" s="14" t="s">
         <v>1114</v>
       </c>
       <c r="B203" s="6" t="s">
@@ -7746,7 +7752,7 @@
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A204" s="14" t="s">
+      <c r="A204" s="12" t="s">
         <v>1115</v>
       </c>
       <c r="B204" s="6" t="s">
@@ -7763,7 +7769,7 @@
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A205" s="14" t="s">
+      <c r="A205" s="12" t="s">
         <v>1116</v>
       </c>
       <c r="B205" s="6" t="s">
@@ -7780,7 +7786,7 @@
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A206" s="14" t="s">
+      <c r="A206" s="12" t="s">
         <v>1117</v>
       </c>
       <c r="B206" s="6" t="s">
@@ -7797,7 +7803,7 @@
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A207" s="14" t="s">
+      <c r="A207" s="12" t="s">
         <v>1118</v>
       </c>
       <c r="B207" s="6" t="s">
@@ -7814,7 +7820,7 @@
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A208" s="14" t="s">
+      <c r="A208" s="12" t="s">
         <v>1119</v>
       </c>
       <c r="B208" s="6" t="s">
@@ -7831,7 +7837,7 @@
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A209" s="14" t="s">
+      <c r="A209" s="12" t="s">
         <v>1120</v>
       </c>
       <c r="B209" s="6" t="s">
@@ -7848,7 +7854,7 @@
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A210" s="14" t="s">
+      <c r="A210" s="12" t="s">
         <v>1121</v>
       </c>
       <c r="B210" s="6" t="s">
@@ -7865,7 +7871,7 @@
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A211" s="14" t="s">
+      <c r="A211" s="12" t="s">
         <v>1122</v>
       </c>
       <c r="B211" s="6" t="s">
@@ -7882,7 +7888,7 @@
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A212" s="14" t="s">
+      <c r="A212" s="12" t="s">
         <v>1123</v>
       </c>
       <c r="B212" s="6" t="s">
@@ -7899,7 +7905,7 @@
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A213" s="14" t="s">
+      <c r="A213" s="12" t="s">
         <v>1124</v>
       </c>
       <c r="B213" s="6" t="s">
@@ -7916,7 +7922,7 @@
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A214" s="14" t="s">
+      <c r="A214" s="12" t="s">
         <v>1125</v>
       </c>
       <c r="B214" s="6" t="s">
@@ -7933,7 +7939,7 @@
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A215" s="14" t="s">
+      <c r="A215" s="12" t="s">
         <v>1126</v>
       </c>
       <c r="B215" s="6" t="s">
@@ -7950,7 +7956,7 @@
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A216" s="14" t="s">
+      <c r="A216" s="12" t="s">
         <v>1127</v>
       </c>
       <c r="B216" s="6" t="s">
@@ -7967,7 +7973,7 @@
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A217" s="14" t="s">
+      <c r="A217" s="12" t="s">
         <v>1128</v>
       </c>
       <c r="B217" s="6" t="s">
@@ -7984,7 +7990,7 @@
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A218" s="14" t="s">
+      <c r="A218" s="12" t="s">
         <v>1129</v>
       </c>
       <c r="B218" s="6" t="s">
@@ -8001,7 +8007,7 @@
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A219" s="14" t="s">
+      <c r="A219" s="12" t="s">
         <v>1130</v>
       </c>
       <c r="B219" s="6" t="s">
@@ -8018,7 +8024,7 @@
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A220" s="14" t="s">
+      <c r="A220" s="12" t="s">
         <v>1131</v>
       </c>
       <c r="B220" s="6" t="s">
@@ -8035,7 +8041,7 @@
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A221" s="14" t="s">
+      <c r="A221" s="12" t="s">
         <v>1132</v>
       </c>
       <c r="B221" s="6" t="s">
@@ -8052,7 +8058,7 @@
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A222" s="17" t="s">
+      <c r="A222" s="15" t="s">
         <v>1133</v>
       </c>
       <c r="B222" s="6" t="s">
@@ -8069,7 +8075,7 @@
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A223" s="14" t="s">
+      <c r="A223" s="12" t="s">
         <v>1134</v>
       </c>
       <c r="B223" s="6" t="s">
@@ -8086,7 +8092,7 @@
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A224" s="14" t="s">
+      <c r="A224" s="12" t="s">
         <v>1135</v>
       </c>
       <c r="B224" s="6" t="s">
@@ -8103,7 +8109,7 @@
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A225" s="14" t="s">
+      <c r="A225" s="12" t="s">
         <v>1136</v>
       </c>
       <c r="B225" s="6" t="s">
@@ -8120,7 +8126,7 @@
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A226" s="14" t="s">
+      <c r="A226" s="12" t="s">
         <v>1137</v>
       </c>
       <c r="B226" s="6" t="s">
@@ -8137,7 +8143,7 @@
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A227" s="14" t="s">
+      <c r="A227" s="12" t="s">
         <v>1138</v>
       </c>
       <c r="B227" s="6" t="s">
@@ -8154,7 +8160,7 @@
       </c>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A228" s="14" t="s">
+      <c r="A228" s="12" t="s">
         <v>1139</v>
       </c>
       <c r="B228" s="6" t="s">
@@ -8171,7 +8177,7 @@
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A229" s="14" t="s">
+      <c r="A229" s="12" t="s">
         <v>1140</v>
       </c>
       <c r="B229" s="6" t="s">
@@ -8188,7 +8194,7 @@
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A230" s="14" t="s">
+      <c r="A230" s="12" t="s">
         <v>1141</v>
       </c>
       <c r="B230" s="6" t="s">
@@ -8205,7 +8211,7 @@
       </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A231" s="14" t="s">
+      <c r="A231" s="12" t="s">
         <v>1142</v>
       </c>
       <c r="B231" s="6" t="s">
@@ -8222,7 +8228,7 @@
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A232" s="14" t="s">
+      <c r="A232" s="12" t="s">
         <v>1143</v>
       </c>
       <c r="B232" s="6" t="s">
@@ -8239,7 +8245,7 @@
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A233" s="14" t="s">
+      <c r="A233" s="12" t="s">
         <v>1144</v>
       </c>
       <c r="B233" s="6" t="s">
@@ -8256,7 +8262,7 @@
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A234" s="14" t="s">
+      <c r="A234" s="12" t="s">
         <v>1145</v>
       </c>
       <c r="B234" s="6" t="s">
@@ -8273,7 +8279,7 @@
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A235" s="14" t="s">
+      <c r="A235" s="12" t="s">
         <v>1146</v>
       </c>
       <c r="B235" s="6" t="s">
@@ -8290,7 +8296,7 @@
       </c>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A236" s="14" t="s">
+      <c r="A236" s="12" t="s">
         <v>1147</v>
       </c>
       <c r="B236" s="6" t="s">
@@ -8307,7 +8313,7 @@
       </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A237" s="14" t="s">
+      <c r="A237" s="12" t="s">
         <v>1148</v>
       </c>
       <c r="B237" s="6" t="s">
@@ -8324,7 +8330,7 @@
       </c>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A238" s="14" t="s">
+      <c r="A238" s="12" t="s">
         <v>1149</v>
       </c>
       <c r="B238" s="6" t="s">
@@ -8341,7 +8347,7 @@
       </c>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A239" s="14" t="s">
+      <c r="A239" s="12" t="s">
         <v>1150</v>
       </c>
       <c r="B239" s="6" t="s">
@@ -8358,7 +8364,7 @@
       </c>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A240" s="14" t="s">
+      <c r="A240" s="12" t="s">
         <v>1151</v>
       </c>
       <c r="B240" s="6" t="s">
@@ -8375,7 +8381,7 @@
       </c>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A241" s="14" t="s">
+      <c r="A241" s="12" t="s">
         <v>1152</v>
       </c>
       <c r="B241" s="6" t="s">
@@ -8392,7 +8398,7 @@
       </c>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A242" s="14" t="s">
+      <c r="A242" s="12" t="s">
         <v>1153</v>
       </c>
       <c r="B242" s="6" t="s">
@@ -8409,7 +8415,7 @@
       </c>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A243" s="14" t="s">
+      <c r="A243" s="12" t="s">
         <v>1154</v>
       </c>
       <c r="B243" s="6" t="s">
@@ -8426,7 +8432,7 @@
       </c>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A244" s="14" t="s">
+      <c r="A244" s="12" t="s">
         <v>1155</v>
       </c>
       <c r="B244" s="6" t="s">
@@ -8443,7 +8449,7 @@
       </c>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A245" s="14" t="s">
+      <c r="A245" s="12" t="s">
         <v>1156</v>
       </c>
       <c r="B245" s="6" t="s">
@@ -8460,7 +8466,7 @@
       </c>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A246" s="14" t="s">
+      <c r="A246" s="12" t="s">
         <v>1157</v>
       </c>
       <c r="B246" s="6" t="s">
@@ -8477,7 +8483,7 @@
       </c>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A247" s="14" t="s">
+      <c r="A247" s="12" t="s">
         <v>1158</v>
       </c>
       <c r="B247" s="6" t="s">
@@ -8494,7 +8500,7 @@
       </c>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A248" s="14" t="s">
+      <c r="A248" s="12" t="s">
         <v>1159</v>
       </c>
       <c r="B248" s="6" t="s">
@@ -8511,7 +8517,7 @@
       </c>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A249" s="14" t="s">
+      <c r="A249" s="12" t="s">
         <v>1160</v>
       </c>
       <c r="B249" s="6" t="s">
@@ -8528,7 +8534,7 @@
       </c>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A250" s="14" t="s">
+      <c r="A250" s="12" t="s">
         <v>1161</v>
       </c>
       <c r="B250" s="6" t="s">
@@ -8545,7 +8551,7 @@
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A251" s="14" t="s">
+      <c r="A251" s="12" t="s">
         <v>1162</v>
       </c>
       <c r="B251" s="6" t="s">
@@ -8562,7 +8568,7 @@
       </c>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A252" s="14" t="s">
+      <c r="A252" s="12" t="s">
         <v>1163</v>
       </c>
       <c r="B252" s="6" t="s">
@@ -8579,7 +8585,7 @@
       </c>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A253" s="14" t="s">
+      <c r="A253" s="12" t="s">
         <v>1164</v>
       </c>
       <c r="B253" s="6" t="s">
@@ -8596,7 +8602,7 @@
       </c>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A254" s="14" t="s">
+      <c r="A254" s="12" t="s">
         <v>1165</v>
       </c>
       <c r="B254" s="6" t="s">
@@ -8613,7 +8619,7 @@
       </c>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A255" s="14" t="s">
+      <c r="A255" s="12" t="s">
         <v>1166</v>
       </c>
       <c r="B255" s="6" t="s">
@@ -8630,7 +8636,7 @@
       </c>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A256" s="14" t="s">
+      <c r="A256" s="12" t="s">
         <v>1167</v>
       </c>
       <c r="B256" s="6" t="s">
@@ -8647,7 +8653,7 @@
       </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A257" s="14" t="s">
+      <c r="A257" s="12" t="s">
         <v>1168</v>
       </c>
       <c r="B257" s="6" t="s">
@@ -8664,7 +8670,7 @@
       </c>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A258" s="14" t="s">
+      <c r="A258" s="12" t="s">
         <v>1169</v>
       </c>
       <c r="B258" s="6" t="s">
@@ -8681,7 +8687,7 @@
       </c>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A259" s="14" t="s">
+      <c r="A259" s="12" t="s">
         <v>1170</v>
       </c>
       <c r="B259" s="6" t="s">
@@ -8698,281 +8704,282 @@
       </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A260" s="18" t="s">
+      <c r="A260" s="16" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B260" s="17" t="s">
         <v>1171</v>
       </c>
-      <c r="B260" s="19" t="s">
+      <c r="C260" s="18" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D260" s="16" t="s">
+        <v>1173</v>
+      </c>
+      <c r="E260" s="7" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A261" s="16" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B261" s="17" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C261" s="18" t="s">
+        <v>1176</v>
+      </c>
+      <c r="D261" s="16" t="s">
+        <v>1177</v>
+      </c>
+      <c r="E261" s="7" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A262" s="16" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B262" s="17" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C262" s="18" t="s">
+        <v>1180</v>
+      </c>
+      <c r="D262" s="8" t="s">
+        <v>1181</v>
+      </c>
+      <c r="E262" s="7" t="s">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A263" s="16" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B263" s="17" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C263" s="18" t="s">
+        <v>1184</v>
+      </c>
+      <c r="D263" s="8" t="s">
+        <v>1185</v>
+      </c>
+      <c r="E263" s="7" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A264" s="16" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B264" s="17" t="s">
         <v>1187</v>
       </c>
-      <c r="C260" s="20" t="s">
+      <c r="C264" s="18" t="s">
         <v>1188</v>
       </c>
-      <c r="D260" s="18" t="s">
+      <c r="D264" s="8" t="s">
         <v>1189</v>
       </c>
-      <c r="E260" s="7" t="s">
+      <c r="E264" s="7" t="s">
         <v>1190</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A261" s="18" t="s">
-        <v>1172</v>
-      </c>
-      <c r="B261" s="19" t="s">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A265" s="16" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B265" s="17" t="s">
         <v>1191</v>
       </c>
-      <c r="C261" s="20" t="s">
+      <c r="C265" s="18" t="s">
         <v>1192</v>
       </c>
-      <c r="D261" s="18" t="s">
+      <c r="D265" s="8" t="s">
         <v>1193</v>
       </c>
-      <c r="E261" s="7" t="s">
+      <c r="E265" s="7" t="s">
         <v>1194</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A262" s="18" t="s">
-        <v>1173</v>
-      </c>
-      <c r="B262" s="19" t="s">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A266" s="16" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B266" s="17" t="s">
         <v>1195</v>
       </c>
-      <c r="C262" s="20" t="s">
+      <c r="C266" s="18" t="s">
         <v>1196</v>
       </c>
-      <c r="D262" s="8" t="s">
+      <c r="D266" s="8" t="s">
         <v>1197</v>
       </c>
-      <c r="E262" s="7" t="s">
+      <c r="E266" s="7" t="s">
         <v>1198</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A263" s="18" t="s">
-        <v>1174</v>
-      </c>
-      <c r="B263" s="19" t="s">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A267" s="16" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B267" s="17" t="s">
         <v>1199</v>
       </c>
-      <c r="C263" s="20" t="s">
+      <c r="C267" s="18" t="s">
         <v>1200</v>
       </c>
-      <c r="D263" s="8" t="s">
+      <c r="D267" s="7" t="s">
         <v>1201</v>
       </c>
-      <c r="E263" s="7" t="s">
+      <c r="E267" s="7" t="s">
         <v>1202</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A264" s="18" t="s">
-        <v>1175</v>
-      </c>
-      <c r="B264" s="19" t="s">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A268" s="16" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B268" s="17" t="s">
         <v>1203</v>
       </c>
-      <c r="C264" s="20" t="s">
+      <c r="C268" s="18" t="s">
         <v>1204</v>
       </c>
-      <c r="D264" s="8" t="s">
+      <c r="D268" s="19" t="s">
         <v>1205</v>
       </c>
-      <c r="E264" s="7" t="s">
+      <c r="E268" s="7" t="s">
         <v>1206</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A265" s="18" t="s">
-        <v>1176</v>
-      </c>
-      <c r="B265" s="19" t="s">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A269" s="16" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B269" s="17" t="s">
         <v>1207</v>
       </c>
-      <c r="C265" s="20" t="s">
+      <c r="C269" s="18" t="s">
         <v>1208</v>
       </c>
-      <c r="D265" s="8" t="s">
+      <c r="D269" s="7" t="s">
         <v>1209</v>
       </c>
-      <c r="E265" s="7" t="s">
+      <c r="E269" s="7" t="s">
         <v>1210</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A266" s="18" t="s">
-        <v>1177</v>
-      </c>
-      <c r="B266" s="19" t="s">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A270" s="16" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B270" s="17" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C270" s="18" t="s">
         <v>1211</v>
       </c>
-      <c r="C266" s="20" t="s">
+      <c r="D270" s="7" t="s">
         <v>1212</v>
       </c>
-      <c r="D266" s="8" t="s">
+      <c r="E270" s="7" t="s">
         <v>1213</v>
       </c>
-      <c r="E266" s="7" t="s">
+    </row>
+    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A271" s="16" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B271" s="17" t="s">
         <v>1214</v>
       </c>
-    </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A267" s="18" t="s">
-        <v>1178</v>
-      </c>
-      <c r="B267" s="19" t="s">
+      <c r="C271" s="18" t="s">
         <v>1215</v>
       </c>
-      <c r="C267" s="20" t="s">
+      <c r="D271" s="7" t="s">
         <v>1216</v>
       </c>
-      <c r="D267" s="7" t="s">
+      <c r="E271" s="7" t="s">
         <v>1217</v>
       </c>
-      <c r="E267" s="7" t="s">
+    </row>
+    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A272" s="16" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B272" s="17" t="s">
         <v>1218</v>
       </c>
-    </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A268" s="18" t="s">
-        <v>1179</v>
-      </c>
-      <c r="B268" s="19" t="s">
+      <c r="C272" s="18" t="s">
         <v>1219</v>
       </c>
-      <c r="C268" s="20" t="s">
+      <c r="D272" s="20" t="s">
         <v>1220</v>
       </c>
-      <c r="D268" s="21" t="s">
+      <c r="E272" s="21" t="s">
         <v>1221</v>
       </c>
-      <c r="E268" s="7" t="s">
+    </row>
+    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A273" s="16" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B273" s="17" t="s">
         <v>1222</v>
       </c>
-    </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A269" s="18" t="s">
-        <v>1180</v>
-      </c>
-      <c r="B269" s="19" t="s">
+      <c r="C273" s="18" t="s">
         <v>1223</v>
       </c>
-      <c r="C269" s="20" t="s">
+      <c r="D273" s="7" t="s">
         <v>1224</v>
       </c>
-      <c r="D269" s="7" t="s">
+      <c r="E273" s="7" t="s">
         <v>1225</v>
       </c>
-      <c r="E269" s="7" t="s">
+    </row>
+    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A274" s="16" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B274" s="17" t="s">
         <v>1226</v>
       </c>
-    </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A270" s="18" t="s">
-        <v>1181</v>
-      </c>
-      <c r="B270" s="19" t="s">
-        <v>1219</v>
-      </c>
-      <c r="C270" s="20" t="s">
+      <c r="C274" s="18" t="s">
         <v>1227</v>
       </c>
-      <c r="D270" s="7" t="s">
+      <c r="D274" s="7" t="s">
         <v>1228</v>
       </c>
-      <c r="E270" s="7" t="s">
+      <c r="E274" s="22" t="s">
         <v>1229</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A271" s="18" t="s">
-        <v>1182</v>
-      </c>
-      <c r="B271" s="19" t="s">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A275" s="16" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B275" s="17" t="s">
         <v>1230</v>
       </c>
-      <c r="C271" s="20" t="s">
+      <c r="C275" s="18" t="s">
         <v>1231</v>
       </c>
-      <c r="D271" s="7" t="s">
+      <c r="D275" s="7" t="s">
         <v>1232</v>
       </c>
-      <c r="E271" s="7" t="s">
+      <c r="E275" s="7" t="s">
         <v>1233</v>
-      </c>
-    </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A272" s="18" t="s">
-        <v>1183</v>
-      </c>
-      <c r="B272" s="19" t="s">
-        <v>1234</v>
-      </c>
-      <c r="C272" s="20" t="s">
-        <v>1235</v>
-      </c>
-      <c r="D272" s="22" t="s">
-        <v>1236</v>
-      </c>
-      <c r="E272" s="23" t="s">
-        <v>1237</v>
-      </c>
-    </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A273" s="18" t="s">
-        <v>1184</v>
-      </c>
-      <c r="B273" s="19" t="s">
-        <v>1238</v>
-      </c>
-      <c r="C273" s="20" t="s">
-        <v>1239</v>
-      </c>
-      <c r="D273" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="E273" s="7" t="s">
-        <v>1241</v>
-      </c>
-    </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A274" s="18" t="s">
-        <v>1185</v>
-      </c>
-      <c r="B274" s="19" t="s">
-        <v>1242</v>
-      </c>
-      <c r="C274" s="20" t="s">
-        <v>1243</v>
-      </c>
-      <c r="D274" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="E274" s="24" t="s">
-        <v>1245</v>
-      </c>
-    </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A275" s="18" t="s">
-        <v>1186</v>
-      </c>
-      <c r="B275" s="19" t="s">
-        <v>1246</v>
-      </c>
-      <c r="C275" s="20" t="s">
-        <v>1247</v>
-      </c>
-      <c r="D275" s="7" t="s">
-        <v>1248</v>
-      </c>
-      <c r="E275" s="7" t="s">
-        <v>1249</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
+  <phoneticPr fontId="11" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="A1" r:id="rId1" xr:uid="{0288513A-A354-4F9A-87C8-4131CA56BCB1}"/>
   </hyperlinks>

--- a/input/excel/Profil and ValueSet_Observation_14.01.2026_v4.csv/ObservationCodesVS.xlsx
+++ b/input/excel/Profil and ValueSet_Observation_14.01.2026_v4.csv/ObservationCodesVS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\behzod_axmedov\Desktop\DHP-temp02\ObservationLab\digital-health-ig\input\excel\Profil and ValueSet_Observation_14.01.2026_v4.csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4E7FEC7-E07C-4C3C-921F-48B16711541B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEA34C7A-70C4-40F4-A1D0-292ED7833152}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1370" uniqueCount="1250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1374" uniqueCount="1254">
   <si>
     <t>https://terminology.dhp.uz/fhir/core/CodeSystem/observation-lab-research-codes-cs/</t>
   </si>
@@ -3798,6 +3798,18 @@
   </si>
   <si>
     <t>lab-258</t>
+  </si>
+  <si>
+    <t>lab-P</t>
+  </si>
+  <si>
+    <t>Gepatit</t>
+  </si>
+  <si>
+    <t>Гепатит</t>
+  </si>
+  <si>
+    <t>Hepatitis</t>
   </si>
 </sst>
 </file>
@@ -4295,7 +4307,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K275"/>
+  <dimension ref="A1:K276"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.140625" customWidth="1"/>
@@ -8704,274 +8716,289 @@
       </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A260" s="16" t="s">
-        <v>1234</v>
-      </c>
-      <c r="B260" s="17" t="s">
-        <v>1171</v>
-      </c>
-      <c r="C260" s="18" t="s">
-        <v>1172</v>
-      </c>
-      <c r="D260" s="16" t="s">
-        <v>1173</v>
+      <c r="A260" s="12" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B260" s="6"/>
+      <c r="C260" s="5" t="s">
+        <v>1251</v>
+      </c>
+      <c r="D260" s="7" t="s">
+        <v>1252</v>
       </c>
       <c r="E260" s="7" t="s">
-        <v>1174</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261" s="16" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="B261" s="17" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="C261" s="18" t="s">
-        <v>1176</v>
+        <v>1172</v>
       </c>
       <c r="D261" s="16" t="s">
-        <v>1177</v>
+        <v>1173</v>
       </c>
       <c r="E261" s="7" t="s">
-        <v>1178</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262" s="16" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="B262" s="17" t="s">
-        <v>1179</v>
+        <v>1175</v>
       </c>
       <c r="C262" s="18" t="s">
-        <v>1180</v>
-      </c>
-      <c r="D262" s="8" t="s">
-        <v>1181</v>
+        <v>1176</v>
+      </c>
+      <c r="D262" s="16" t="s">
+        <v>1177</v>
       </c>
       <c r="E262" s="7" t="s">
-        <v>1182</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263" s="16" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="B263" s="17" t="s">
-        <v>1183</v>
+        <v>1179</v>
       </c>
       <c r="C263" s="18" t="s">
-        <v>1184</v>
+        <v>1180</v>
       </c>
       <c r="D263" s="8" t="s">
-        <v>1185</v>
+        <v>1181</v>
       </c>
       <c r="E263" s="7" t="s">
-        <v>1186</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264" s="16" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="B264" s="17" t="s">
-        <v>1187</v>
+        <v>1183</v>
       </c>
       <c r="C264" s="18" t="s">
-        <v>1188</v>
+        <v>1184</v>
       </c>
       <c r="D264" s="8" t="s">
-        <v>1189</v>
+        <v>1185</v>
       </c>
       <c r="E264" s="7" t="s">
-        <v>1190</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A265" s="16" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="B265" s="17" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="C265" s="18" t="s">
-        <v>1192</v>
+        <v>1188</v>
       </c>
       <c r="D265" s="8" t="s">
-        <v>1193</v>
+        <v>1189</v>
       </c>
       <c r="E265" s="7" t="s">
-        <v>1194</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266" s="16" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="B266" s="17" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="C266" s="18" t="s">
-        <v>1196</v>
+        <v>1192</v>
       </c>
       <c r="D266" s="8" t="s">
-        <v>1197</v>
+        <v>1193</v>
       </c>
       <c r="E266" s="7" t="s">
-        <v>1198</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A267" s="16" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="B267" s="17" t="s">
-        <v>1199</v>
+        <v>1195</v>
       </c>
       <c r="C267" s="18" t="s">
-        <v>1200</v>
-      </c>
-      <c r="D267" s="7" t="s">
-        <v>1201</v>
+        <v>1196</v>
+      </c>
+      <c r="D267" s="8" t="s">
+        <v>1197</v>
       </c>
       <c r="E267" s="7" t="s">
-        <v>1202</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A268" s="16" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="B268" s="17" t="s">
-        <v>1203</v>
+        <v>1199</v>
       </c>
       <c r="C268" s="18" t="s">
-        <v>1204</v>
-      </c>
-      <c r="D268" s="19" t="s">
-        <v>1205</v>
+        <v>1200</v>
+      </c>
+      <c r="D268" s="7" t="s">
+        <v>1201</v>
       </c>
       <c r="E268" s="7" t="s">
-        <v>1206</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A269" s="16" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="B269" s="17" t="s">
-        <v>1207</v>
+        <v>1203</v>
       </c>
       <c r="C269" s="18" t="s">
-        <v>1208</v>
-      </c>
-      <c r="D269" s="7" t="s">
-        <v>1209</v>
+        <v>1204</v>
+      </c>
+      <c r="D269" s="19" t="s">
+        <v>1205</v>
       </c>
       <c r="E269" s="7" t="s">
-        <v>1210</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A270" s="16" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="B270" s="17" t="s">
-        <v>1203</v>
+        <v>1207</v>
       </c>
       <c r="C270" s="18" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="D270" s="7" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="E270" s="7" t="s">
-        <v>1213</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A271" s="16" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="B271" s="17" t="s">
-        <v>1214</v>
+        <v>1203</v>
       </c>
       <c r="C271" s="18" t="s">
-        <v>1215</v>
+        <v>1211</v>
       </c>
       <c r="D271" s="7" t="s">
-        <v>1216</v>
+        <v>1212</v>
       </c>
       <c r="E271" s="7" t="s">
-        <v>1217</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A272" s="16" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="B272" s="17" t="s">
-        <v>1218</v>
+        <v>1214</v>
       </c>
       <c r="C272" s="18" t="s">
-        <v>1219</v>
-      </c>
-      <c r="D272" s="20" t="s">
-        <v>1220</v>
-      </c>
-      <c r="E272" s="21" t="s">
-        <v>1221</v>
+        <v>1215</v>
+      </c>
+      <c r="D272" s="7" t="s">
+        <v>1216</v>
+      </c>
+      <c r="E272" s="7" t="s">
+        <v>1217</v>
       </c>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A273" s="16" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="B273" s="17" t="s">
-        <v>1222</v>
+        <v>1218</v>
       </c>
       <c r="C273" s="18" t="s">
-        <v>1223</v>
-      </c>
-      <c r="D273" s="7" t="s">
-        <v>1224</v>
-      </c>
-      <c r="E273" s="7" t="s">
-        <v>1225</v>
+        <v>1219</v>
+      </c>
+      <c r="D273" s="20" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E273" s="21" t="s">
+        <v>1221</v>
       </c>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A274" s="16" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="B274" s="17" t="s">
-        <v>1226</v>
+        <v>1222</v>
       </c>
       <c r="C274" s="18" t="s">
-        <v>1227</v>
+        <v>1223</v>
       </c>
       <c r="D274" s="7" t="s">
-        <v>1228</v>
-      </c>
-      <c r="E274" s="22" t="s">
-        <v>1229</v>
+        <v>1224</v>
+      </c>
+      <c r="E274" s="7" t="s">
+        <v>1225</v>
       </c>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A275" s="16" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B275" s="17" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C275" s="18" t="s">
+        <v>1227</v>
+      </c>
+      <c r="D275" s="7" t="s">
+        <v>1228</v>
+      </c>
+      <c r="E275" s="22" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A276" s="16" t="s">
         <v>1249</v>
       </c>
-      <c r="B275" s="17" t="s">
+      <c r="B276" s="17" t="s">
         <v>1230</v>
       </c>
-      <c r="C275" s="18" t="s">
+      <c r="C276" s="18" t="s">
         <v>1231</v>
       </c>
-      <c r="D275" s="7" t="s">
+      <c r="D276" s="7" t="s">
         <v>1232</v>
       </c>
-      <c r="E275" s="7" t="s">
+      <c r="E276" s="7" t="s">
         <v>1233</v>
       </c>
     </row>
